--- a/data/2026-09/flujo_licitaciones_2026-09-11.xlsx
+++ b/data/2026-09/flujo_licitaciones_2026-09-11.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sin Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="✅ Adjudicados con CUIT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🔗 Flujo Cruzado" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,40 +414,880 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>estado</t>
+          <t>fecha_extraccion</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>fecha</t>
+          <t>fecha_publicacion</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>detalle</t>
+          <t>organismo_contratante</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tipo_proceso</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>aviso_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>proveedor_adjudicado</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>cuit_proveedor</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>monto_adjudicado</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>texto_muestra</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>fuente</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sin datos — todos los servicios externos fallaron</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11 11:27</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BORA / Comprar / TGN no respondieron. Reintentar mañana.</t>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL OESTE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Licitación Pública 04/2025</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2417323</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417323/20260911</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>30-70746458-1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>$15.660.000</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/pdf/linkQR/cDYraDdDNmxmVzFSbkVWUVVZR3c4dz09
+AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -
+DIRECCIÓN REGIONAL OESTE
+Licitación Pública 04/2025
+Expediente  N°:  EX-2025-00811645-  -ARCA-SGCFDVADMO#SDGOPIM  Objeto  de  la  contratación:
+Servicio de mantenimiento corre</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE SEMILLAS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Licitación Pública 2/2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2417324</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417324/20260911</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MAC S.R.L.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>30-64640840-3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/pdf/linkQR/RElGQnBtY05EVmhSbkVWUVVZR3c4dz09
+INSTITUTO NACIONAL DE SEMILLAS
+Licitación Pública 2/2026
+UOC: 50 - Departamento de Compras y Contrataciones Ejercicio: 2026 Clase: Única Nacional Modalidad:
+Sin modalidad Expediente N°: EX-2026-38975612- -APN-DA#INASE O</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA HIDROVÍA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Licitación Pública 41/2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2417325</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417325/20260911</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>OBRAS CIVILES GZCRON S.A</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>30-71595775-9</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>$247.265.000,00</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/pdf/linkQR/SmNJUDVYaWpKdEpSbkVWUVVZR3c4dz09
+AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -
+DIRECCIÓN REGIONAL ADUANERA HIDROVÍA
+Licitación Pública 41/2026
+Ejercicio:  2026  Expediente  Nº:  EX-2026-01971887-  -ARCA-SECFDVAFHI#SDGOAI  Objeto  de  la
+contratación: “AD</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Licitación Pública 482/2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2417326</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417326/20260911</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TUX SA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>30-71434715-9</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>$39.457.800,00</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/pdf/linkQR/bDBCc1JlaXphaU5SbkVWUVVZR3c4dz09
+EJÉRCITO ARGENTINO
+Licitación Pública 482/2026
+UOC: 84/40 - Comando Brigada Mecanizada X Ejercicio: 2026 Clase: Única Nacional Modalidad: Orden
+de compra abierta Expediente N°: EX-2026-66020573- -APN-CBMX#EA Objeto: ADQ</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>organismo_contratante</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tipo_proceso_bora</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>link_bora</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>proveedor_adjudicado</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>cuit_proveedor</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>monto_adjudicado_bora</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>en_comprar</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>procesos_comprar</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>unidad_comprar</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>nro_proceso_comprar</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>cobro_en_tgn</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>beneficiario_tgn</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>monto_cobrado_tgn</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>metodo_cruce_tgn</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>etapa</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>indicadores_riesgo</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>score_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>indice_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>nivel_riesgo_licit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIBLIOTECA DEL CONGRESO DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Licitación Pública 002/26</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417321/20260911</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>BANCO PATAGONIA S.A</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EMPRESA ARGENTINA DE NAVEGACIÓN AÉREA S.E.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Licitación Pública (Modo IV) 06/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417322/20260911</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL OESTE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Licitación Pública 04/2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417323/20260911</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30-70746458-1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>$15.660.000</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>✅ ADJUDICADO (sin pago aún)</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE SEMILLAS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Licitación Pública 2/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417324/20260911</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MAC S.R.L.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30-64640840-3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>✅ ADJUDICADO (sin pago aún)</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA HIDROVÍA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Licitación Pública 41/2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417325/20260911</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>OBRAS CIVILES GZCRON S.A</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>30-71595775-9</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>$247.265.000,00</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>✅ ADJUDICADO (sin pago aún)</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>🟡 Monto Límite ($247,265,000 justo bajo el tope de 5,000 módulos)</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Licitación Pública 482/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417326/20260911</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TUX SA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30-71434715-9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>$39.457.800,00</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>✅ ADJUDICADO (sin pago aún)</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bajo</t>
         </is>
       </c>
     </row>
